--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512404_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512404_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.22</v>
+        <v>2.9003</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7382</v>
+        <v>2.7893</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4818</v>
+        <v>0.111</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6465</v>
+        <v>4.6454</v>
       </c>
       <c r="H2" t="n">
-        <v>4.089</v>
+        <v>4.0917</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5574</v>
+        <v>0.5537</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8951</v>
+        <v>4.9694</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3128</v>
+        <v>4.3659</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.6036</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2486</v>
+        <v>-0.3241</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2238</v>
+        <v>-0.2742</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0248</v>
+        <v>-0.0499</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8474</v>
+        <v>-0.4979</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3461</v>
+        <v>0.2817</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4987</v>
+        <v>-0.7796</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.4544</v>
+        <v>-0.4374</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.4544</v>
+        <v>-0.4374</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. MUNOZ SAMATAN</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5904</v>
+        <v>0.5926</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2249</v>
+        <v>0.5926</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6345</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4571</v>
+        <v>0.5926</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1371</v>
+        <v>0.5926</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.68</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0763</v>
+        <v>0.5926</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9183</v>
+        <v>0.5926</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1581</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6192</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7812</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.838</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8194</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2048</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0242</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6861</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6466</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0395</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>D. MUNOZ SAMATAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5855</v>
+        <v>0.5128</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5855</v>
+        <v>1.6572</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1.1444</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5855</v>
+        <v>0.4236</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5855</v>
+        <v>1.1272</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-0.7037</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5855</v>
+        <v>2.1141</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5855</v>
+        <v>1.9551</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-1.6905</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.8278</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.8627</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.8098</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.2025</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.0123</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.7206</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.2545</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.4661</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.8641</v>
+        <v>0.4367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5907</v>
+        <v>1.6938</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.4548</v>
+        <v>-1.2572</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5782</v>
+        <v>2.5777</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9314</v>
+        <v>1.9181</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6468</v>
+        <v>0.6596</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8594</v>
+        <v>2.9244</v>
       </c>
       <c r="K5" t="n">
-        <v>1.932</v>
+        <v>1.9557</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9274</v>
+        <v>0.9686</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2812</v>
+        <v>-0.3467</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0376</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2806</v>
+        <v>-0.309</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.2617</v>
+        <v>-0.9508</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2445</v>
+        <v>-0.2183</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.0172</v>
+        <v>-0.7326</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0295</v>
+        <v>-0.8449</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3122</v>
+        <v>-1.1248</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2827</v>
+        <v>0.2799</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9182</v>
+        <v>-0.9327</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.028</v>
+        <v>-0.039</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8901</v>
+        <v>-0.8938</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2609</v>
+        <v>-0.2804</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.028</v>
+        <v>-0.039</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2329</v>
+        <v>-0.2414</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.521</v>
+        <v>-0.3171</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.655</v>
+        <v>-0.4725</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1339</v>
+        <v>0.1554</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. GATELL SANZ</t>
+          <t>D. ARJOL LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3752</v>
+        <v>-2.9884</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7583</v>
+        <v>-2.3271</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6169</v>
+        <v>-0.6613</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.4826</v>
+        <v>-0.9919</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5382</v>
+        <v>-1.0082</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.9445</v>
+        <v>0.0163</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5144</v>
+        <v>0.7956</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1034</v>
+        <v>0.1758</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6177</v>
+        <v>0.6198</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9683</v>
+        <v>-1.7875</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6415</v>
+        <v>-1.184</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3267</v>
+        <v>-0.6036</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S7" t="n">
-        <v>1.288</v>
+        <v>-0.8708</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9852</v>
+        <v>-0.7823</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3029</v>
+        <v>-0.0885</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.1806</v>
+        <v>-1.1257</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-1.1257</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. ARJOL LOPEZ</t>
+          <t>J. JIMENEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.161</v>
+        <v>-3.7864</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6779</v>
+        <v>-2.9305</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.483</v>
+        <v>-0.8559</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.984</v>
+        <v>-3.53</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.009</v>
+        <v>-1.4436</v>
       </c>
       <c r="I8" t="n">
-        <v>0.025</v>
+        <v>-2.0864</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7417</v>
+        <v>-1.9528</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1345</v>
+        <v>-1.1089</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6072</v>
+        <v>-0.8439</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7257</v>
+        <v>-1.5772</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1434</v>
+        <v>-0.3346</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-1.2425</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.4049</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2291</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2291</v>
+        <v>1.4172</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0261</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0396</v>
+        <v>0.1278</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0136</v>
+        <v>-0.6958</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1509</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.1509</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. JIMENEZ JIMENEZ</t>
+          <t>E. GATELL SANZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.8491</v>
+        <v>-3.8066</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9289</v>
+        <v>-1.5816</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9202</v>
+        <v>-2.225</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5304</v>
+        <v>-2.5286</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4548</v>
+        <v>-0.5527</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0756</v>
+        <v>-1.9758</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.0131</v>
+        <v>-0.4947</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1478</v>
+        <v>0.1179</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8653</v>
+        <v>-0.6126</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5173</v>
+        <v>-2.0339</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.307</v>
+        <v>-0.6706</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2103</v>
+        <v>-1.3633</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4097</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0242</v>
+        <v>-1.2147</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4339</v>
+        <v>1.2147</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6222</v>
+        <v>-0.0878</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2146</v>
+        <v>0.1278</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8368</v>
+        <v>-0.2156</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1062</v>
+        <v>-1.1902</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1062</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8075</v>
+        <v>-4.4413</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9352</v>
+        <v>-3.7029</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8723</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4119</v>
+        <v>-1.4183</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7841</v>
+        <v>-1.7981</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3722</v>
+        <v>0.3798</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8387</v>
+        <v>-0.7819</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7242</v>
+        <v>-0.6934</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1145</v>
+        <v>-0.0885</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.6363</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0599</v>
+        <v>-1.1047</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4868</v>
+        <v>0.4684</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2533</v>
+        <v>-2.227</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8258</v>
+        <v>-1.4482</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8431</v>
+        <v>-0.694</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9827</v>
+        <v>-0.7542</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1359</v>
+        <v>-0.1577</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1359</v>
+        <v>-0.1577</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4871</v>
+        <v>-4.4635</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3078</v>
+        <v>-4.5137</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1793</v>
+        <v>0.0502</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.5976</v>
+        <v>-3.5786</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.1043</v>
+        <v>-2.0958</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4933</v>
+        <v>-1.4828</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.2515</v>
+        <v>-4.2055</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6895</v>
+        <v>-2.6696</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5621</v>
+        <v>-1.536</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6539</v>
+        <v>0.6269</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.5738</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0687</v>
+        <v>0.0531</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2862</v>
+        <v>-0.2535</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8515</v>
+        <v>-0.1057</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4348</v>
+        <v>-0.1478</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.624700000000001</v>
+        <v>-8.248799999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.7259</v>
+        <v>-5.5313</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8987</v>
+        <v>-2.7175</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.0824</v>
+        <v>-5.0971</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0793</v>
+        <v>-2.0757</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0031</v>
+        <v>-3.0214</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.7287</v>
+        <v>-2.6706</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.4932</v>
+        <v>-1.4454</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2355</v>
+        <v>-1.2252</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3537</v>
+        <v>-2.4265</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.586</v>
+        <v>-0.6303</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7677</v>
+        <v>-1.7962</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4452</v>
+        <v>-1.1026</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0809</v>
+        <v>-0.0019</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.3644</v>
+        <v>-1.1007</v>
       </c>
       <c r="V12" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-24.8023</v>
+        <v>-24.1375</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.5069</v>
+        <v>-14.979</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.295199999999999</v>
+        <v>-9.1586</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.739800000000002</v>
+        <v>-9.837900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2547</v>
+        <v>-1.283499999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.485200000000001</v>
+        <v>-8.554500000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1543999999999999</v>
+        <v>0.6383000000000005</v>
       </c>
       <c r="K13" t="n">
-        <v>2.931800000000001</v>
+        <v>3.245699999999998</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.7774</v>
+        <v>-2.6075</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.8941</v>
+        <v>-10.4762</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.186199999999999</v>
+        <v>-4.529</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.7077</v>
+        <v>-5.9471</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.315</v>
+        <v>-13.1595</v>
       </c>
       <c r="R13" t="n">
-        <v>10.2423</v>
+        <v>10.1227</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.538899999999999</v>
+        <v>-6.817299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.8153</v>
+        <v>-1.9919</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.7237</v>
+        <v>-4.8255</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.450700000000001</v>
+        <v>-4.4453</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.5308999999999999</v>
+        <v>-0.4661</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.9198</v>
+        <v>-3.9792</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>A. MOODY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.6096</v>
+        <v>6.8875</v>
       </c>
       <c r="E14" t="n">
-        <v>4.927</v>
+        <v>5.5964</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6826</v>
+        <v>1.291</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9836</v>
+        <v>3.3086</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3946</v>
+        <v>-0.1765</v>
       </c>
       <c r="I14" t="n">
-        <v>1.589</v>
+        <v>3.4851</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5154</v>
+        <v>4.0656</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3429</v>
+        <v>0.513</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1726</v>
+        <v>3.5527</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4681</v>
+        <v>-0.757</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9483</v>
+        <v>-0.6894</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4164</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6145</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2291</v>
+        <v>-2.0245</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8436</v>
+        <v>2.0245</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0115</v>
+        <v>1.2917</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6407</v>
+        <v>1.2681</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3709</v>
+        <v>0.0236</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>2.2872</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.2872</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MOODY</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.2303</v>
+        <v>6.3064</v>
       </c>
       <c r="E15" t="n">
-        <v>5.1478</v>
+        <v>3.55</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0825</v>
+        <v>2.7564</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>3.9952</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1482</v>
+        <v>2.4108</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4481</v>
+        <v>1.5844</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9895</v>
+        <v>3.5797</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4937</v>
+        <v>3.3972</v>
       </c>
       <c r="L15" t="n">
-        <v>3.4959</v>
+        <v>0.1825</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6896</v>
+        <v>0.4155</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6418</v>
+        <v>-0.9864000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0477</v>
+        <v>1.4019</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.0485</v>
+        <v>-1.2147</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0485</v>
+        <v>1.8221</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6753</v>
+        <v>1.7039</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9517</v>
+        <v>1.185</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2764</v>
+        <v>0.5189</v>
       </c>
       <c r="V15" t="n">
-        <v>2.255</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.255</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5241</v>
+        <v>3.7575</v>
       </c>
       <c r="E16" t="n">
-        <v>0.73</v>
+        <v>1.3096</v>
       </c>
       <c r="F16" t="n">
-        <v>2.794</v>
+        <v>2.4478</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7529</v>
+        <v>1.7464</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8864</v>
+        <v>-0.8894</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6393</v>
+        <v>2.6357</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0896</v>
+        <v>1.1333</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.412</v>
+        <v>-0.3773</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5016</v>
+        <v>1.5107</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6633</v>
+        <v>0.613</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4744</v>
+        <v>-0.512</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1377</v>
+        <v>1.1251</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7842</v>
+        <v>1.0473</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1547</v>
+        <v>0.3787</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9389</v>
+        <v>0.6686</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9911</v>
+        <v>3.462</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4271</v>
+        <v>2.4509</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5639999999999999</v>
+        <v>1.0112</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7845</v>
+        <v>1.8083</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5906</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.3751</v>
+        <v>2.3824</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9344</v>
+        <v>2.0081</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7199</v>
+        <v>0.7684</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2145</v>
+        <v>1.2396</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1499</v>
+        <v>-0.1998</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3106</v>
+        <v>-1.3425</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1606</v>
+        <v>1.1428</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0224</v>
+        <v>0.439</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5073</v>
+        <v>0.4428</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5152</v>
+        <v>-0.0037</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>W. CABRAL BUERIBERI</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9389</v>
+        <v>2.1661</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5264</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4653</v>
+        <v>2.0888</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3509</v>
+        <v>-1.1953</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1332</v>
+        <v>-1.9962</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7824</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3482</v>
+        <v>-0.8914</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6877</v>
+        <v>-1.3269</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3395</v>
+        <v>0.4355</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0026</v>
+        <v>-0.3039</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4455</v>
+        <v>-0.6693</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4429</v>
+        <v>0.3654</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6145</v>
+        <v>2.0245</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4339</v>
+        <v>2.0245</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7185</v>
+        <v>1.2437</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6897</v>
+        <v>0.9687</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0288</v>
+        <v>0.275</v>
       </c>
       <c r="V18" t="n">
-        <v>0.4841</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4841</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9022</v>
+        <v>1.5797</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0716</v>
+        <v>0.3017</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8306</v>
+        <v>1.2779</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2083</v>
+        <v>1.1752</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9902</v>
+        <v>0.0003</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7819</v>
+        <v>1.1749</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9875</v>
+        <v>1.5183</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3762</v>
+        <v>-0.2779</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3887</v>
+        <v>1.7962</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2209</v>
+        <v>-0.3431</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6141</v>
+        <v>0.2782</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3932</v>
+        <v>-0.6213</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0485</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.2147</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0485</v>
+        <v>1.2147</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9558</v>
+        <v>0.6554</v>
       </c>
       <c r="T19" t="n">
-        <v>1.059</v>
+        <v>-0.0019</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1032</v>
+        <v>0.6573</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1062</v>
+        <v>-0.2509</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1062</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>W. CABRAL BUERIBERI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.648</v>
+        <v>1.2644</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3452</v>
+        <v>-0.576</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3028</v>
+        <v>1.8404</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4664</v>
+        <v>0.4051</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4153</v>
+        <v>2.1912</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8818</v>
+        <v>-1.7861</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.4537</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6108</v>
+        <v>1.7746</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1185</v>
+        <v>-1.3209</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1957</v>
+        <v>-0.0486</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1954</v>
+        <v>0.4166</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0003</v>
+        <v>-0.4651</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>-2.0245</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4097</v>
+        <v>1.4172</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0325</v>
+        <v>0.9647</v>
       </c>
       <c r="T20" t="n">
-        <v>1.6401</v>
+        <v>0.4929</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3923</v>
+        <v>0.4718</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6965</v>
+        <v>0.5019</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5019</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7241</v>
+        <v>0.4275</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6135</v>
+        <v>0.3388</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3376</v>
+        <v>0.0888</v>
       </c>
       <c r="G21" t="n">
-        <v>1.168</v>
+        <v>-0.4844</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0055</v>
+        <v>0.4151</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1625</v>
+        <v>-0.8996</v>
       </c>
       <c r="J21" t="n">
-        <v>1.467</v>
+        <v>0.7508</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3007</v>
+        <v>0.6315</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7677</v>
+        <v>0.1193</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.299</v>
+        <v>-1.2352</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3062</v>
+        <v>-0.2164</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6051</v>
+        <v>-1.0188</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2291</v>
+        <v>-1.0123</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2291</v>
+        <v>0.4049</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2019</v>
+        <v>0.831</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8515</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6496</v>
+        <v>0.2307</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2421</v>
+        <v>0.6883</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2421</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0363</v>
+        <v>0.3815</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.492</v>
+        <v>-0.13</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5282</v>
+        <v>0.5115</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1395</v>
+        <v>0.1435</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0668</v>
+        <v>0.0597</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0727</v>
+        <v>0.0839</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0505</v>
+        <v>-0.0328</v>
       </c>
       <c r="K22" t="n">
-        <v>0.039</v>
+        <v>0.0395</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0895</v>
+        <v>-0.0723</v>
       </c>
       <c r="M22" t="n">
-        <v>0.19</v>
+        <v>0.1763</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0278</v>
+        <v>0.0202</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1623</v>
+        <v>0.1561</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6145</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1852</v>
+        <v>0.157</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.393</v>
+        <v>-0.0728</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2078</v>
+        <v>0.2298</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W22" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3984</v>
+        <v>-0.3672</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7623</v>
+        <v>-0.7561</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3638</v>
+        <v>0.3889</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2787</v>
+        <v>-0.2768</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4181</v>
+        <v>0.4153</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4181</v>
+        <v>0.4153</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4181</v>
+        <v>0.4153</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3246</v>
+        <v>-0.2928</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0655</v>
+        <v>-0.064</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2591</v>
+        <v>-0.2288</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4037</v>
+        <v>-0.3954</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9593</v>
+        <v>-3.0041</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5556</v>
+        <v>2.6087</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5632</v>
+        <v>-0.5728</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2226</v>
+        <v>-0.215</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4445</v>
+        <v>-1.4172</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6187</v>
+        <v>-0.6131</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8258</v>
+        <v>-0.8041</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6587</v>
+        <v>0.6294</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0555</v>
+        <v>0.0403</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6032</v>
+        <v>0.5891</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4097</v>
+        <v>-0.4049</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0953</v>
+        <v>0.109</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2857</v>
+        <v>-0.3722</v>
       </c>
       <c r="U24" t="n">
-        <v>0.381</v>
+        <v>0.4812</v>
       </c>
       <c r="V24" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6965</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>24.8025</v>
+        <v>25.47</v>
       </c>
       <c r="E25" t="n">
-        <v>8.295200000000001</v>
+        <v>9.1585</v>
       </c>
       <c r="F25" t="n">
-        <v>16.507</v>
+        <v>16.3114</v>
       </c>
       <c r="G25" t="n">
-        <v>9.7402</v>
+        <v>9.838000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2549</v>
+        <v>1.2834</v>
       </c>
       <c r="I25" t="n">
-        <v>8.485000000000001</v>
+        <v>8.554500000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>9.894100000000002</v>
+        <v>10.476</v>
       </c>
       <c r="K25" t="n">
-        <v>4.186399999999999</v>
+        <v>4.529000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>5.7079</v>
+        <v>5.9471</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1542999999999999</v>
+        <v>-0.6381000000000003</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.9315</v>
+        <v>-3.2454</v>
       </c>
       <c r="O25" t="n">
-        <v>2.7774</v>
+        <v>2.6076</v>
       </c>
       <c r="P25" t="n">
-        <v>3.0728</v>
+        <v>3.0367</v>
       </c>
       <c r="Q25" t="n">
-        <v>-10.2424</v>
+        <v>-10.1226</v>
       </c>
       <c r="R25" t="n">
-        <v>13.315</v>
+        <v>13.1595</v>
       </c>
       <c r="S25" t="n">
-        <v>7.539</v>
+        <v>8.149900000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>4.723499999999999</v>
+        <v>4.8256</v>
       </c>
       <c r="U25" t="n">
-        <v>2.8154</v>
+        <v>3.3244</v>
       </c>
       <c r="V25" t="n">
-        <v>4.4506</v>
+        <v>4.445399999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>3.9197</v>
+        <v>3.9793</v>
       </c>
       <c r="X25" t="n">
-        <v>0.5309</v>
+        <v>0.4661</v>
       </c>
     </row>
   </sheetData>
